--- a/data/meta_faturamento_televendas.xlsx
+++ b/data/meta_faturamento_televendas.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\christian.roque\Desktop\convenção\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8D1C6B-F67B-47FD-9EEE-4D4D0D92ADD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696B8BD5-A19A-49D3-B601-9DFE61976926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$117</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -1662,7 +1665,7 @@
         <v>2476</v>
       </c>
       <c r="C112" s="8">
-        <v>232</v>
+        <v>232000</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1673,7 +1676,7 @@
         <v>2494</v>
       </c>
       <c r="C113" s="8">
-        <v>151</v>
+        <v>151000</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1684,7 +1687,7 @@
         <v>2661</v>
       </c>
       <c r="C114" s="8">
-        <v>198</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1695,7 +1698,7 @@
         <v>3465</v>
       </c>
       <c r="C115" s="8">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1706,7 +1709,7 @@
         <v>1133</v>
       </c>
       <c r="C116" s="8">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1717,7 +1720,7 @@
         <v>3467</v>
       </c>
       <c r="C117" s="8">
-        <v>90</v>
+        <v>90000</v>
       </c>
     </row>
   </sheetData>

--- a/data/meta_faturamento_televendas.xlsx
+++ b/data/meta_faturamento_televendas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\christian.roque\Desktop\convenção\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696B8BD5-A19A-49D3-B601-9DFE61976926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C39F7EF-2BCE-4DA1-908D-82E11F3B06B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,19 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$117</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -94,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -123,6 +134,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,15 +440,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -447,7 +461,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>46204</v>
       </c>
@@ -457,8 +471,9 @@
       <c r="C2" s="8">
         <v>330000</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2"/>
+    </row>
+    <row r="3" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>46204</v>
       </c>
@@ -468,8 +483,9 @@
       <c r="C3" s="8">
         <v>275000</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D3"/>
+    </row>
+    <row r="4" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>46204</v>
       </c>
@@ -479,8 +495,9 @@
       <c r="C4" s="8">
         <v>230000</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D4"/>
+    </row>
+    <row r="5" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>46204</v>
       </c>
@@ -490,8 +507,9 @@
       <c r="C5" s="8">
         <v>120000</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D5"/>
+    </row>
+    <row r="6" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>46204</v>
       </c>
@@ -501,8 +519,9 @@
       <c r="C6" s="8">
         <v>160000</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D6"/>
+    </row>
+    <row r="7" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>46204</v>
       </c>
@@ -512,8 +531,9 @@
       <c r="C7" s="8">
         <v>140000</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D7"/>
+    </row>
+    <row r="8" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>46204</v>
       </c>
@@ -523,8 +543,9 @@
       <c r="C8" s="8">
         <v>270000</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D8"/>
+    </row>
+    <row r="9" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>46204</v>
       </c>
@@ -534,8 +555,9 @@
       <c r="C9" s="8">
         <v>320000</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D9"/>
+    </row>
+    <row r="10" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>46204</v>
       </c>
@@ -545,8 +567,9 @@
       <c r="C10" s="8">
         <v>260000</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D10"/>
+    </row>
+    <row r="11" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>46204</v>
       </c>
@@ -556,8 +579,9 @@
       <c r="C11" s="8">
         <v>262000</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D11"/>
+    </row>
+    <row r="12" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>46204</v>
       </c>
@@ -567,8 +591,9 @@
       <c r="C12" s="8">
         <v>265000</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D12"/>
+    </row>
+    <row r="13" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>46204</v>
       </c>
@@ -578,8 +603,9 @@
       <c r="C13" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D13"/>
+    </row>
+    <row r="14" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>46204</v>
       </c>
@@ -589,8 +615,9 @@
       <c r="C14" s="8">
         <v>250000</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D14"/>
+    </row>
+    <row r="15" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>46204</v>
       </c>
@@ -600,8 +627,9 @@
       <c r="C15" s="8">
         <v>250000</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D15"/>
+    </row>
+    <row r="16" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>46204</v>
       </c>
@@ -611,8 +639,9 @@
       <c r="C16" s="8">
         <v>330000</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D16"/>
+    </row>
+    <row r="17" spans="1:3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>46204</v>
       </c>
@@ -623,7 +652,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>46204</v>
       </c>
@@ -634,7 +663,7 @@
         <v>370000</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>46204</v>
       </c>
@@ -645,7 +674,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>46204</v>
       </c>
@@ -656,7 +685,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>46204</v>
       </c>
@@ -667,7 +696,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>46204</v>
       </c>
@@ -678,7 +707,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>46204</v>
       </c>
@@ -689,7 +718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>46204</v>
       </c>
@@ -700,7 +729,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>46204</v>
       </c>
@@ -711,7 +740,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>46204</v>
       </c>
@@ -722,7 +751,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>46204</v>
       </c>
@@ -733,7 +762,7 @@
         <v>290000</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>46204</v>
       </c>
@@ -744,7 +773,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>46204</v>
       </c>
@@ -755,7 +784,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>46204</v>
       </c>
@@ -766,7 +795,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>46204</v>
       </c>
@@ -777,7 +806,7 @@
         <v>225000</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>46204</v>
       </c>
@@ -788,7 +817,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>46204</v>
       </c>
@@ -799,7 +828,7 @@
         <v>265000</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>46204</v>
       </c>
@@ -810,7 +839,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>46204</v>
       </c>
@@ -821,7 +850,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>46204</v>
       </c>
@@ -832,7 +861,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>46204</v>
       </c>
@@ -843,7 +872,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>46204</v>
       </c>
@@ -854,7 +883,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>46204</v>
       </c>
@@ -865,7 +894,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>46204</v>
       </c>
@@ -876,7 +905,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>46204</v>
       </c>
@@ -887,7 +916,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>46204</v>
       </c>
@@ -898,7 +927,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>46204</v>
       </c>
@@ -909,7 +938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>46204</v>
       </c>
@@ -920,7 +949,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>46204</v>
       </c>
@@ -931,7 +960,7 @@
         <v>235000</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>46204</v>
       </c>
@@ -942,7 +971,7 @@
         <v>122000</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>46204</v>
       </c>
@@ -953,7 +982,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>46204</v>
       </c>
@@ -964,7 +993,7 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>46204</v>
       </c>
@@ -975,7 +1004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>46204</v>
       </c>
@@ -986,7 +1015,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>46204</v>
       </c>
@@ -997,7 +1026,7 @@
         <v>132000</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>46204</v>
       </c>
@@ -1008,7 +1037,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>46204</v>
       </c>
@@ -1019,7 +1048,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>46204</v>
       </c>
@@ -1030,7 +1059,7 @@
         <v>260000</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>46204</v>
       </c>
@@ -1041,7 +1070,7 @@
         <v>118978.44500000001</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>46204</v>
       </c>
@@ -1052,7 +1081,7 @@
         <v>258470.41500000004</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>46204</v>
       </c>
@@ -1063,7 +1092,7 @@
         <v>209237.95500000005</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>46204</v>
       </c>
@@ -1074,7 +1103,7 @@
         <v>233854.18500000003</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>46204</v>
       </c>
@@ -1085,7 +1114,7 @@
         <v>177024.2</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>46204</v>
       </c>
@@ -1096,7 +1125,7 @@
         <v>132768.15</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>46204</v>
       </c>
@@ -1107,7 +1136,7 @@
         <v>115065.73000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>46204</v>
       </c>
@@ -1118,7 +1147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>46204</v>
       </c>
@@ -1129,7 +1158,7 @@
         <v>247833.88000000003</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>46204</v>
       </c>
@@ -1247,7 +1276,7 @@
         <v>546</v>
       </c>
       <c r="C74" s="8">
-        <v>265000</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1665,7 +1694,7 @@
         <v>2476</v>
       </c>
       <c r="C112" s="8">
-        <v>232000</v>
+        <v>192000</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1676,7 +1705,7 @@
         <v>2494</v>
       </c>
       <c r="C113" s="8">
-        <v>151000</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1687,7 +1716,7 @@
         <v>2661</v>
       </c>
       <c r="C114" s="8">
-        <v>198000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1698,7 +1727,7 @@
         <v>3465</v>
       </c>
       <c r="C115" s="8">
-        <v>90000</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1709,7 +1738,7 @@
         <v>1133</v>
       </c>
       <c r="C116" s="8">
-        <v>90000</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1720,7 +1749,7 @@
         <v>3467</v>
       </c>
       <c r="C117" s="8">
-        <v>90000</v>
+        <v>92000</v>
       </c>
     </row>
   </sheetData>
